--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14701,7 +14701,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17263,7 +17263,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18239,7 +18239,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18422,7 +18422,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22509,7 +22509,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23119,7 +23119,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27999,7 +27999,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30073,7 +30073,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30195,7 +30195,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32208,7 +32208,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32269,7 +32269,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32574,7 +32574,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34221,7 +34221,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34953,7 +34953,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35441,7 +35441,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35456,7 +35456,7 @@
       </c>
       <c r="K574" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L574" t="inlineStr">
@@ -35506,7 +35506,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35567,7 +35567,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35628,7 +35628,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35689,7 +35689,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35811,7 +35811,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35872,7 +35872,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35933,7 +35933,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35994,7 +35994,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36055,7 +36055,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36177,7 +36177,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36238,7 +36238,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36299,7 +36299,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36360,7 +36360,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36421,7 +36421,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36482,7 +36482,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36543,7 +36543,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36604,7 +36604,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36787,7 +36787,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36848,7 +36848,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36909,7 +36909,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36970,7 +36970,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37031,7 +37031,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37092,7 +37092,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37153,7 +37153,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37214,7 +37214,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37275,7 +37275,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37397,7 +37397,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37519,7 +37519,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37641,7 +37641,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37702,7 +37702,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37763,7 +37763,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37824,7 +37824,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37885,7 +37885,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38129,7 +38129,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38190,7 +38190,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38251,7 +38251,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38373,7 +38373,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38434,7 +38434,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38495,7 +38495,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38556,7 +38556,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38617,7 +38617,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38678,7 +38678,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38922,7 +38922,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39105,7 +39105,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39288,7 +39288,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39349,7 +39349,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39532,7 +39532,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39593,7 +39593,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39715,7 +39715,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39776,7 +39776,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39898,7 +39898,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39959,7 +39959,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40081,7 +40081,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40203,7 +40203,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40264,7 +40264,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40386,7 +40386,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40447,7 +40447,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40569,7 +40569,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40813,7 +40813,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40874,7 +40874,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40935,7 +40935,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40996,7 +40996,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41057,7 +41057,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41118,7 +41118,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41240,7 +41240,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41301,7 +41301,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41362,7 +41362,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41545,7 +41545,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41667,7 +41667,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41789,7 +41789,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41850,7 +41850,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41911,7 +41911,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41972,7 +41972,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42094,7 +42094,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42155,7 +42155,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42216,7 +42216,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42277,7 +42277,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42338,7 +42338,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42399,7 +42399,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42460,7 +42460,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42521,7 +42521,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42643,7 +42643,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42704,7 +42704,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42765,7 +42765,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42887,7 +42887,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -42948,7 +42948,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43009,7 +43009,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43070,7 +43070,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43131,7 +43131,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43192,7 +43192,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43314,7 +43314,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43375,7 +43375,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43436,7 +43436,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43497,7 +43497,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43558,7 +43558,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -43619,7 +43619,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43680,7 +43680,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -43741,7 +43741,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -43802,7 +43802,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -43863,7 +43863,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -43924,7 +43924,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -43985,7 +43985,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44046,7 +44046,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -44107,7 +44107,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44168,7 +44168,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44229,7 +44229,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44351,7 +44351,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -44412,7 +44412,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -44473,7 +44473,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44534,7 +44534,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -44595,7 +44595,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -44656,7 +44656,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -44839,7 +44839,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -44900,7 +44900,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -44961,7 +44961,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -45022,7 +45022,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -45083,7 +45083,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45144,7 +45144,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45205,7 +45205,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45327,7 +45327,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45388,7 +45388,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45449,7 +45449,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45510,7 +45510,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -45571,7 +45571,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45693,7 +45693,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45754,7 +45754,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45815,7 +45815,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -45876,7 +45876,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -45937,7 +45937,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -45998,7 +45998,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46059,7 +46059,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46120,7 +46120,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46242,7 +46242,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -46303,7 +46303,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46364,7 +46364,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -46486,7 +46486,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -46669,7 +46669,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -46730,7 +46730,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -46791,7 +46791,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -46852,7 +46852,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -46913,7 +46913,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -46974,7 +46974,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47035,7 +47035,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -47096,7 +47096,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -47157,7 +47157,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -47218,7 +47218,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -47279,7 +47279,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -47340,7 +47340,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -47401,7 +47401,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -47462,7 +47462,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -47523,7 +47523,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -47584,7 +47584,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -47645,7 +47645,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -47767,7 +47767,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -47828,7 +47828,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -47889,7 +47889,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -48011,7 +48011,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -48072,7 +48072,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -48133,7 +48133,7 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -48194,7 +48194,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -48255,7 +48255,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -48316,7 +48316,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -48438,7 +48438,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -48499,7 +48499,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -48560,7 +48560,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -48682,7 +48682,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -48743,7 +48743,7 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -48865,7 +48865,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -48926,7 +48926,7 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1322,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1509,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1704,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1891,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1956,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2021,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2147,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2212,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2277,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2342,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2529,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2899,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2964,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3151,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3216,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3464,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3655,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3781,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3846,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3911,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3976,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4041,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4228,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4293,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4358,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4423,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4488,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4553,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4740,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4805,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4931,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5240,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5488,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5553,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5740,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5866,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5931,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6057,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6427,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6492,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6557,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6622,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6687,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6752,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7061,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7187,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7374,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7439,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7504,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7691,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7756,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7821,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7951,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8077,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8142,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8207,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8272,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8337,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8524,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8772,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8837,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9085,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9150,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9215,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9280,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9345,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9410,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9475,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9601,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9666,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9792,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9918,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +9983,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10048,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10174,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10239,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10304,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10430,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10556,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10621,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10747,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10934,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11060,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11125,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11190,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11255,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11320,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11385,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11450,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11698,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +11885,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12011,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12076,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12202,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12389,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12454,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12519,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12584,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12649,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +12714,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12779,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12844,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12909,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12974,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13039,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13165,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13291,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13356,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13421,11 @@
           <t>8.306.984-8</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13486,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13551,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13616,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13681,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13807,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +13872,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14059,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14185,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14311,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14376,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14441,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14506,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14571,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14636,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14701,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14766,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +14953,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15018,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15083,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15148,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15213,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15400,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15526,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15591,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15656,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +15843,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15969,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16034,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16221,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16347,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16534,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +16599,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +16664,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16729,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16794,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16981,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17046,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17355,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17481,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17546,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17672,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17737,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17985,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18050,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18176,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18241,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18306,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18493,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18619,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18745,11 @@
           <t>76.905.483-9</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +18993,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19058,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19184,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19249,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19314,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19379,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19505,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19631,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19696,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +19761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19826,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19891,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20017,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20147,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20212,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20338,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20403,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20594,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20842,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21212,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21277,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21342,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +21472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21537,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +21602,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22277,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22342,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22468,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22594,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22659,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +22785,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +22850,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +22915,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +22980,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23045,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23110,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23419,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23606,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +23732,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23919,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +23984,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24232,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24419,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24484,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +24610,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +24736,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +24862,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +24988,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25053,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25179,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25244,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25309,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25374,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +25439,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +25504,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +25569,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25634,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +25760,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +25886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +25951,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26142,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26207,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26272,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +26398,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +26524,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26589,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +26837,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +26902,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +26967,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27032,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27158,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27223,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27288,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27353,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +27601,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27727,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +27853,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +27918,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +27983,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28109,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28296,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +28361,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28426,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +28491,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28678,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +28865,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +28930,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +28995,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29060,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +29247,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29434,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +29499,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +29564,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +29690,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +29755,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29820,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +29885,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +29950,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30015,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30080,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30145,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30210,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +30275,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30401,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +30527,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +30653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +30718,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30783,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +30848,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +30913,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31100,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +31226,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31291,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31478,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31543,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31608,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +31673,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +31738,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +31803,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +31868,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +31933,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +31998,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32063,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32189,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32315,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32380,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32445,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32632,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +32697,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +32823,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +32888,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +32953,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33079,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33144,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +33209,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +33335,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +33400,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33465,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +33530,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +33595,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +33660,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +33908,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +33973,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34038,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34103,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +34168,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +34233,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +34298,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34485,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +34550,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +34615,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +34680,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +34745,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +34810,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +34997,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35123,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +35371,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +35436,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35501,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34417,7 +35749,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34478,7 +35814,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34539,7 +35879,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +35944,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34661,7 +36009,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34722,7 +36074,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +36139,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +36204,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34905,7 +36269,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36456,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35149,7 +36521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36586,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35271,7 +36651,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +36903,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +36968,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +37216,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36190,7 +37586,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +37712,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +37777,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +37842,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36556,7 +37968,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36678,7 +38094,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +38159,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +38224,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +38289,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +38415,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +38541,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +38667,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37288,7 +38732,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +38858,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37471,7 +38923,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +38988,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +39053,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +39118,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +39183,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +39248,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +39435,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +39500,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38081,7 +39565,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +39630,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +39756,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +39821,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +39886,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38447,7 +39951,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40016,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +40142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38874,7 +40390,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +40455,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39118,7 +40642,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +40890,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +40955,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39484,7 +41020,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +41085,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +41211,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39728,7 +41276,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +41341,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39850,7 +41406,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39911,7 +41471,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39972,7 +41536,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40033,7 +41601,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40155,7 +41727,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40216,7 +41792,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40460,7 +42040,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40521,7 +42105,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40643,7 +42231,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40765,7 +42357,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40948,7 +42544,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41131,7 +42731,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41192,7 +42796,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41314,7 +42922,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41375,7 +42987,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41436,7 +43052,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41497,7 +43117,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41558,7 +43182,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41619,7 +43247,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41680,7 +43312,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41741,7 +43377,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41802,7 +43442,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41863,7 +43507,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41985,7 +43633,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42107,7 +43759,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42290,7 +43946,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42412,7 +44072,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42473,7 +44137,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42595,7 +44263,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42656,7 +44328,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42717,7 +44393,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42778,7 +44458,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42839,7 +44523,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42900,7 +44588,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42961,7 +44653,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43022,7 +44718,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43083,7 +44783,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43327,7 +45031,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43388,7 +45096,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43449,7 +45161,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43571,7 +45287,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43693,7 +45413,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43876,7 +45600,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43998,7 +45726,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44120,7 +45852,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44181,7 +45917,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44364,7 +46104,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44486,7 +46230,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44669,7 +46417,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44791,7 +46543,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44852,7 +46608,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44913,7 +46673,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44974,7 +46738,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45096,7 +46864,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45157,7 +46929,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45279,7 +47055,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45462,7 +47242,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45584,7 +47368,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45645,7 +47433,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45706,7 +47498,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45767,7 +47563,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45828,7 +47628,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45889,7 +47693,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46011,7 +47819,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46072,7 +47884,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46133,7 +47949,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46194,7 +48014,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46316,7 +48140,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46499,7 +48327,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46560,7 +48392,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46621,7 +48457,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46682,7 +48522,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46743,7 +48587,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46804,7 +48652,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46865,7 +48717,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46926,7 +48782,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K762" t="inlineStr"/>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L762" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47048,7 +48908,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47109,7 +48973,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47170,7 +49038,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47292,7 +49164,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47536,7 +49412,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47597,7 +49477,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47658,7 +49542,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L774" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47780,7 +49668,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47963,7 +49855,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48329,7 +50225,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48390,7 +50290,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L786" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48451,7 +50355,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K787" t="inlineStr"/>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L787" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48695,7 +50603,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48756,7 +50668,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48817,7 +50733,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48878,7 +50798,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48939,7 +50863,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49000,7 +50928,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L796" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/abr-2025.xlsx
@@ -3090,7 +3090,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4618,7 +4622,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4996,7 +5004,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5305,7 +5317,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5618,7 +5634,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5996,7 +6016,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6183,7 +6207,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6939,7 +6967,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8463,7 +8495,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8589,7 +8625,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8650,7 +8690,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10113,7 +10157,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10812,7 +10860,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12141,7 +12193,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12328,7 +12384,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13746,7 +13806,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14831,7 +14895,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15339,7 +15407,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15721,7 +15793,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16473,7 +16549,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17233,7 +17313,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17863,7 +17947,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18115,7 +18203,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18558,7 +18650,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18684,7 +18780,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20659,7 +20759,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20907,7 +21011,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21728,7 +21836,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21789,7 +21901,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21972,7 +22088,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23545,7 +23665,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23797,7 +23921,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24110,7 +24238,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26337,7 +26469,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26776,7 +26912,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27418,7 +27558,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27666,7 +27810,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27792,7 +27940,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28174,7 +28326,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28804,7 +28960,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29312,7 +29472,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32254,7 +32418,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33847,7 +34015,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35627,7 +35799,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35688,7 +35864,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36395,7 +36575,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37094,7 +37278,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37907,7 +38095,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38033,7 +38225,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38354,7 +38550,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38797,7 +38997,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39313,7 +39517,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40081,7 +40289,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40520,7 +40732,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40829,7 +41045,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41857,7 +42077,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42422,7 +42646,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43885,7 +44113,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44909,7 +45141,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46295,7 +46531,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46482,7 +46722,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46803,7 +47047,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48266,7 +48514,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49351,7 +49603,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49981,7 +50237,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L781" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50042,7 +50302,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
